--- a/Data informations.xlsx
+++ b/Data informations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A065BDA9-ACAC-4546-9CAC-60A6C2783875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8573CB3F-8CB1-4F5C-B2C1-ACE648FA1F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{21385BF3-0849-44D0-97B4-3D3D0322C3DA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="57">
   <si>
     <t>Year</t>
   </si>
@@ -208,48 +208,6 @@
   </si>
   <si>
     <t>End-of-Life</t>
-  </si>
-  <si>
-    <t>PV systems number</t>
-  </si>
-  <si>
-    <t>Total number of installed PV systems</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>PDGD</t>
-  </si>
-  <si>
-    <t>Historical + projected data</t>
-  </si>
-  <si>
-    <t>Module weight</t>
-  </si>
-  <si>
-    <t>Total mass of installed PV modules</t>
-  </si>
-  <si>
-    <t>tonnes</t>
-  </si>
-  <si>
-    <t>Estimated from installed capacity</t>
-  </si>
-  <si>
-    <t>Premature disposal potential</t>
-  </si>
-  <si>
-    <t>Estimated fraction of systems subject to premature disposal</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>IEA-PVPS</t>
-  </si>
-  <si>
-    <t>Fixed at 23% of Module weight</t>
   </si>
 </sst>
 </file>
@@ -257,7 +215,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -317,27 +275,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -658,1478 +607,1478 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>23431.379400000002</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>23431.379400000002</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2">
         <v>23431.379400000002</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2">
         <v>18428.400000000001</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2">
         <v>18428.400000000001</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2">
         <v>18428.400000000001</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2">
         <v>5002.9794000000002</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2">
         <v>5002.9794000000002</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2">
         <v>5002.9794000000002</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2">
         <v>5002.9794000000002</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2">
         <v>5002.9794000000002</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2">
         <v>5002.9794000000002</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>23255.278162860632</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>23255.278162860632</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3">
         <v>23255.278162860632</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3">
         <v>18612.684000000001</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>18520.542000000001</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>18437.6142</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3">
         <v>4642.594162860627</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3">
         <v>9645.5735628606271</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3">
         <v>4734.7361628606268</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3">
         <v>9737.715562860627</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3">
         <v>4817.6639628606281</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3">
         <v>9820.6433628606283</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>23080.500434900659</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>23080.500434900659</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4">
         <v>23080.500434900659</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>18798.810839999998</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>18613.14471</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4">
         <v>18446.833007099998</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4">
         <v>4281.6895949006584</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4">
         <v>13927.263157761279</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4">
         <v>4467.3557249006626</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4">
         <v>14205.07128776129</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4">
         <v>4633.6674278006576</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4">
         <v>14454.31079066129</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>22907.036269134049</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>22907.036269134049</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>22907.036269134049</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5">
         <v>18986.798948399999</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>18706.21043354999</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5">
         <v>18456.05642360355</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5">
         <v>3920.2373207340461</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5">
         <v>17847.500478495331</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5">
         <v>4200.8258355840553</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5">
         <v>18405.897123345341</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5">
         <v>4450.9798455305026</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5">
         <v>18905.290636191789</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>22734.875793332489</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>22734.875793332489</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>22734.875793332489</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>19176.666937884002</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>18799.741485717739</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6">
         <v>18465.284451815351</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>3558.208855448484</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6">
         <v>21405.709333943811</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6">
         <v>3935.1343076147418</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6">
         <v>22341.031430960091</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6">
         <v>4269.5913415171381</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6">
         <v>23174.88197770893</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>22564.009209463511</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>22564.009209463511</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>22564.009209463511</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7">
         <v>19368.433607262839</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7">
         <v>18893.740193146328</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7">
         <v>18474.51709404125</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7">
         <v>3195.575602200664</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7">
         <v>24601.284936144479</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7">
         <v>3670.2690163171792</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7">
         <v>26011.30044727727</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7">
         <v>4089.4921154222538</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7">
         <v>27264.37409313118</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>22394.42679313292</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8">
         <v>22394.42679313292</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8">
         <v>22394.42679313292</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8">
         <v>19562.11794333547</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8">
         <v>18988.20889411206</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <v>18483.754352588279</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8">
         <v>2832.30884979745</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8">
         <v>27433.593785941928</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8">
         <v>3406.2178990208631</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8">
         <v>29417.518346298129</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8">
         <v>3910.672440544648</v>
       </c>
-      <c r="M8" s="1">
+      <c r="M8">
         <v>31175.046533675832</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>22226.118893031318</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9">
         <v>22226.118893031318</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>22226.118893031318</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9">
         <v>19757.73912276882</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9">
         <v>19083.149938582621</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <v>18492.996229764569</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>2468.3797702624979</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9">
         <v>29901.97355620443</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9">
         <v>3142.968954448701</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9">
         <v>32560.48730074683</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9">
         <v>3733.1226632667531</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9">
         <v>34908.169196942581</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
         <v>22059.07593038485</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10">
         <v>22059.07593038485</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>22059.07593038485</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10">
         <v>19955.31651399652</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>19178.565688275528</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10">
         <v>18502.242727879449</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10">
         <v>2103.75941638833</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10">
         <v>32005.732972592759</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10">
         <v>2880.5102421093138</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10">
         <v>35440.997542856137</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10">
         <v>3556.8332025053969</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M10">
         <v>38465.002399447978</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
         <v>21893.288398410001</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>21893.288398410001</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>21893.288398410001</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <v>20154.869679136478</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <v>19274.458516716899</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11">
         <v>18511.49384924339</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <v>1738.418719273526</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11">
         <v>33744.151691866282</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11">
         <v>2618.8298816931019</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11">
         <v>38059.82742454925</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11">
         <v>3381.7945491666142</v>
       </c>
-      <c r="M11" s="1">
+      <c r="M11">
         <v>41846.796948614588</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12">
         <v>21728.746861772641</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <v>21728.746861772641</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>21728.746861772641</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>20356.418375927838</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12">
         <v>19370.830809300489</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12">
         <v>18520.749596168011</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12">
         <v>1372.3284858447951</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12">
         <v>35116.480177711077</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12">
         <v>2357.9160524721478</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12">
         <v>40417.743477021402</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12">
         <v>3207.997265604627</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M12">
         <v>45054.794214219219</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13">
         <v>21565.44195605093</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13">
         <v>21565.44195605093</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>21565.44195605093</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13">
         <v>20559.98255968712</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13">
         <v>19467.68496334699</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13">
         <v>18530.00997096609</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13">
         <v>1005.459396363814</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13">
         <v>36121.939574074888</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13">
         <v>2097.756992703944</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K13">
         <v>42515.500469725353</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13">
         <v>3035.4319850848442</v>
       </c>
-      <c r="M13" s="1">
+      <c r="M13">
         <v>48090.226199304059</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14">
         <v>21403.36438720247</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14">
         <v>21403.36438720247</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14">
         <v>21403.36438720247</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14">
         <v>20765.582385283989</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14">
         <v>19565.023388163721</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14">
         <v>18539.274975951579</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14">
         <v>637.78200191848009</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14">
         <v>36759.721575993368</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14">
         <v>1838.340999038752</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K14">
         <v>44353.841468764098</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14">
         <v>2864.0894112508981</v>
       </c>
-      <c r="M14" s="1">
+      <c r="M14">
         <v>50954.315610554957</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
         <v>21242.504931035281</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <v>21242.504931035281</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15">
         <v>21242.504931035281</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15">
         <v>20973.238209136831</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15">
         <v>19662.848505104539</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15">
         <v>18548.54461343955</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15">
         <v>269.26672189844248</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15">
         <v>37028.98829789181</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15">
         <v>1579.6564259307379</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K15">
         <v>45933.497894694839</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15">
         <v>2693.9603175957268</v>
       </c>
-      <c r="M15" s="1">
+      <c r="M15">
         <v>53648.275928150688</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16">
         <v>21082.85443268286</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16">
         <v>21082.85443268286</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16">
         <v>21082.85443268286</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16">
         <v>21182.970591228201</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16">
         <v>19761.16274763006</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16">
         <v>18557.81888574627</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16">
         <v>-100.1161585453447</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16">
         <v>36928.872139346473</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16">
         <v>1321.691685052803</v>
       </c>
-      <c r="K16" s="1">
+      <c r="K16">
         <v>47255.189579747654</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16">
         <v>2525.0355469365932</v>
       </c>
-      <c r="M16" s="1">
+      <c r="M16">
         <v>56173.311475087277</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17">
         <v>20924.403806083181</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17">
         <v>20924.403806083181</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17">
         <v>20924.403806083181</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17">
         <v>21394.800297140489</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17">
         <v>19859.968561368209</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17">
         <v>18567.09779518914</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17">
         <v>-470.39649105730132</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17">
         <v>36458.475648289168</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17">
         <v>1064.4352447149761</v>
       </c>
-      <c r="K17" s="1">
+      <c r="K17">
         <v>48319.624824462619</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17">
         <v>2357.306010894044</v>
       </c>
-      <c r="M17" s="1">
+      <c r="M17">
         <v>58530.617485981318</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18">
         <v>20767.144033461551</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18">
         <v>20767.144033461551</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18">
         <v>20767.144033461551</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18">
         <v>21608.748300111889</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18">
         <v>19959.268404175051</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18">
         <v>18576.381344086731</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18">
         <v>-841.6042666503381</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18">
         <v>35616.871381638834</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18">
         <v>807.87562928650732</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K18">
         <v>49127.500453749133</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18">
         <v>2190.7626893748202</v>
       </c>
-      <c r="M18" s="1">
+      <c r="M18">
         <v>60721.380175356142</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19">
         <v>20611.066164817421</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19">
         <v>20611.066164817421</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19">
         <v>20611.066164817421</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19">
         <v>21824.835783113009</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19">
         <v>20059.06474619592</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19">
         <v>18585.66953475877</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19">
         <v>-1213.769618295591</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19">
         <v>34403.101763343242</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19">
         <v>552.00141862150122</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19">
         <v>49679.501872370631</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19">
         <v>2025.396630058643</v>
       </c>
-      <c r="M19" s="1">
+      <c r="M19">
         <v>62746.776805414789</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20">
         <v>20456.161317414972</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20">
         <v>20456.161317414972</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20">
         <v>20456.161317414972</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20">
         <v>22043.084140944138</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20">
         <v>20159.36006992689</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20">
         <v>18594.962369526151</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20">
         <v>-1586.9228235291671</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20">
         <v>32816.178939814083</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20">
         <v>296.80124748807788</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20">
         <v>49976.303119858712</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20">
         <v>1861.1989478888211</v>
       </c>
-      <c r="M20" s="1">
+      <c r="M20">
         <v>64607.97575330361</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21">
         <v>20302.420675277641</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21">
         <v>20302.420675277641</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21">
         <v>20302.420675277641</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21">
         <v>22263.514982353579</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21">
         <v>20260.156870276529</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21">
         <v>18604.259850710911</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21">
         <v>-1961.094307075939</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21">
         <v>30855.08463273814</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21">
         <v>42.263805001115543</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21">
         <v>50018.566924859828</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21">
         <v>1698.1608245667269</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M21">
         <v>66306.136577870333</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22">
         <v>20149.835488686349</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22">
         <v>20149.835488686349</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22">
         <v>20149.835488686349</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22">
         <v>22486.150132177121</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22">
         <v>20361.45765462791</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22">
         <v>18613.56198063627</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22">
         <v>-2336.3146434907721</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22">
         <v>28518.769989247361</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22">
         <v>-211.6221659415605</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22">
         <v>49806.944758918267</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22">
         <v>1536.273508050075</v>
       </c>
-      <c r="M22" s="1">
+      <c r="M22">
         <v>67842.410085920405</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23">
         <v>19998.397073681532</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23">
         <v>19998.397073681532</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23">
         <v>19998.397073681532</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23">
         <v>22711.011633498889</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23">
         <v>20463.264942901049</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23">
         <v>18622.868761626589</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23">
         <v>-2712.6145598173612</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23">
         <v>25806.15542943</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23">
         <v>-464.86786921951722</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23">
         <v>49342.07688969875</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23">
         <v>1375.5283120549429</v>
       </c>
-      <c r="M23" s="1">
+      <c r="M23">
         <v>69217.938397975347</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24">
         <v>19848.096811568928</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24">
         <v>19848.096811568928</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24">
         <v>19848.096811568928</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24">
         <v>22938.121749833881</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24">
         <v>20565.581267615551</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24">
         <v>18632.180196007401</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24">
         <v>-3090.0249382649449</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24">
         <v>22716.130491165059</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24">
         <v>-717.48445604661538</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K24">
         <v>48624.592433652128</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L24">
         <v>1215.916615561531</v>
       </c>
-      <c r="M24" s="1">
+      <c r="M24">
         <v>70433.855013536871</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25">
         <v>19698.92614842908</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25">
         <v>19698.92614842908</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25">
         <v>19698.92614842908</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25">
         <v>23167.502967332221</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25">
         <v>20668.40917395362</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25">
         <v>18641.496286105401</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25">
         <v>-3468.5768189031369</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25">
         <v>19247.553672261922</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25">
         <v>-969.48302552454334</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K25">
         <v>47655.109408127602</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L25">
         <v>1057.4298623236789</v>
       </c>
-      <c r="M25" s="1">
+      <c r="M25">
         <v>71491.284875860554</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26">
         <v>19550.876594630488</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26">
         <v>19550.876594630488</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26">
         <v>19550.876594630488</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26">
         <v>23399.17799700554</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26">
         <v>20771.751219823389</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26">
         <v>18650.817034248459</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26">
         <v>-3848.301402375047</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26">
         <v>15399.252269886871</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26">
         <v>-1220.8746251928969</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K26">
         <v>46434.234782934698</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L26">
         <v>900.05956038203658</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M26">
         <v>72391.344436242594</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27">
         <v>19403.939724346459</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27">
         <v>19403.939724346459</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27">
         <v>19403.939724346459</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27">
         <v>23633.169776975588</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27">
         <v>20875.6099759225</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27">
         <v>18660.14244276558</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27">
         <v>-4229.2300526291292</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27">
         <v>11170.022217257751</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27">
         <v>-1471.670251576041</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K27">
         <v>44962.564531358657</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L27">
         <v>743.79728158088619</v>
       </c>
-      <c r="M27" s="1">
+      <c r="M27">
         <v>73135.141717823484</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28">
         <v>19258.10717507558</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28">
         <v>19258.10717507558</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28">
         <v>19258.10717507558</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28">
         <v>23869.50147474535</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28">
         <v>20979.988025802118</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28">
         <v>18669.472513986959</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28">
         <v>-4611.394299669777</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28">
         <v>6558.6279175879681</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28">
         <v>-1721.8808507265419</v>
       </c>
-      <c r="K28" s="1">
+      <c r="K28">
         <v>43240.683680632123</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L28">
         <v>588.63466108861394</v>
       </c>
-      <c r="M28" s="1">
+      <c r="M28">
         <v>73723.776378912095</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29">
         <v>19113.370647165761</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29">
         <v>19113.370647165761</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29">
         <v>19113.370647165761</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29">
         <v>24108.19648949281</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29">
         <v>21084.887965931121</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29">
         <v>18678.80725024395</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29">
         <v>-4994.8258423270418</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29">
         <v>1563.8020752609259</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29">
         <v>-1971.51731876536</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K29">
         <v>41269.166361866752</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L29">
         <v>434.56339692181058</v>
       </c>
-      <c r="M29" s="1">
+      <c r="M29">
         <v>74158.339775833912</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30">
         <v>18969.72190334195</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30">
         <v>18969.72190334195</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30">
         <v>18969.72190334195</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30">
         <v>24349.278454387731</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30">
         <v>21190.312405760771</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30">
         <v>18688.146653869069</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30">
         <v>-5379.5565510457818</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30">
         <v>-3815.754475784855</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30">
         <v>-2220.5905024188251</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K30">
         <v>39048.575859447927</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30">
         <v>281.57524947287669</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M30">
         <v>74439.915025306793</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31">
         <v>18827.152768237229</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31">
         <v>18827.152768237229</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31">
         <v>18827.152768237229</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31">
         <v>24592.771238931611</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31">
         <v>21296.263967789579</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31">
         <v>18697.490727196011</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31">
         <v>-5765.6184706943786</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I31">
         <v>-9581.3729464792341</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31">
         <v>-2469.1111995523461</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K31">
         <v>36579.464659895581</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L31">
         <v>129.66204104122519</v>
       </c>
-      <c r="M31" s="1">
+      <c r="M31">
         <v>74569.577066348022</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32">
         <v>18685.65512792765</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32">
         <v>18685.65512792765</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32">
         <v>18685.65512792765</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32">
         <v>24838.69895132093</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32">
         <v>21402.745287628521</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32">
         <v>18706.839472559601</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32">
         <v>-6153.0438233932764</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I32">
         <v>-15734.41676987251</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32">
         <v>-2717.0901597008742</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K32">
         <v>33862.37450019471</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L32">
         <v>-21.184344631954449</v>
       </c>
-      <c r="M32" s="1">
+      <c r="M32">
         <v>74548.392721716067</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33">
         <v>18545.220929470361</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33">
         <v>18545.220929470361</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33">
         <v>18545.220929470361</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33">
         <v>25087.085940834138</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33">
         <v>21509.759014066669</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33">
         <v>18716.19289229588</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H33">
         <v>-6541.8650113637814</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I33">
         <v>-22276.281781236288</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33">
         <v>-2964.5380845963082</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K33">
         <v>30897.836415598402</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L33">
         <v>-170.9719628255225</v>
       </c>
-      <c r="M33" s="1">
+      <c r="M33">
         <v>74377.420758890541</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34">
         <v>18405.842180445328</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34">
         <v>18405.842180445328</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34">
         <v>18405.842180445328</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34">
         <v>25337.956800242471</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34">
         <v>21617.307809137001</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34">
         <v>18725.55098874203</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34">
         <v>-6932.114619797143</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I34">
         <v>-29208.396401033431</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34">
         <v>-3211.4656286916652</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K34">
         <v>27686.37078690674</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L34">
         <v>-319.70880829669841</v>
       </c>
-      <c r="M34" s="1">
+      <c r="M34">
         <v>74057.711950593846</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35">
         <v>18267.510948500509</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35">
         <v>18267.510948500509</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35">
         <v>18267.510948500509</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35">
         <v>25591.336368244902</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35">
         <v>21725.394348182679</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35">
         <v>18734.9137642364</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35">
         <v>-7323.825419744393</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I35">
         <v>-36532.221820777828</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35">
         <v>-3457.8833996821668</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K35">
         <v>24228.48738722457</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L35">
         <v>-467.40281573589158</v>
       </c>
-      <c r="M35" s="1">
+      <c r="M35">
         <v>73590.309134857962</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36">
         <v>18130.219360900341</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36">
         <v>18130.219360900341</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36">
         <v>18130.219360900341</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36">
         <v>25847.24973192735</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36">
         <v>21834.021319923591</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36">
         <v>18744.281221118519</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36">
         <v>-7717.0303710270164</v>
       </c>
-      <c r="I36" s="1">
+      <c r="I36">
         <v>-44249.252191804837</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36">
         <v>-3703.8019590232511</v>
       </c>
-      <c r="K36" s="1">
+      <c r="K36">
         <v>20524.685428201319</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L36">
         <v>-614.06186021817848</v>
       </c>
-      <c r="M36" s="1">
+      <c r="M36">
         <v>72976.247274639783</v>
       </c>
     </row>
@@ -2145,68 +2094,67 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2">
         <v>13.73</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2">
         <v>29.58</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2">
         <v>11.73</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>19.170000000000002</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3">
         <v>29.58</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3">
         <v>17.170000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>29.86</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4">
         <v>29.58</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <v>27.58</v>
       </c>
     </row>
@@ -2221,184 +2169,184 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="2">
         <v>41275</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2">
         <v>197</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2">
         <v>56.16</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2">
         <v>12.9168</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="2">
         <v>41640</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>491</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3">
         <v>108.21599999999999</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>24.889679999999998</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="2">
         <v>42005</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>1822</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>375.70499999999998</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>86.412149999999997</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="2">
         <v>42370</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>8236</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>1587.1949999999999</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>365.05484999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="2">
         <v>42736</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>21556</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>4537.3769999999986</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>1043.59671</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="2">
         <v>43101</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>57248</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>13198.68</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>3035.6963999999998</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="2">
         <v>43466</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>179019</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>49969.548000000003</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>11492.99604</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="2">
         <v>43831</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>402669</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>114255.981</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9">
         <v>26278.875629999999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="2">
         <v>44197</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>856255</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <v>250556.94899999999</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>57628.098270000002</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="2">
         <v>44562</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>1654988</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <v>509543.81099999999</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>117195.07653000001</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="2">
         <v>44927</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>2337780</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <v>746188.55099999998</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12">
         <v>171623.36673000001</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="2">
         <v>45292</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>3186308</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13">
         <v>1062574.902</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13">
         <v>244392.22745999999</v>
       </c>
     </row>
@@ -2409,7 +2357,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273888D3-5A07-47A3-BE28-64ED8A51ED3B}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -2417,343 +2365,292 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="4" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
